--- a/plantilla_documentos.xlsx
+++ b/plantilla_documentos.xlsx
@@ -17,9 +17,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="dd-mm-yyyy"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="dd-mm-yyyy"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -63,14 +62,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -508,7 +508,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>77.123.456-7</t>
+          <t>77.123.456-9</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -516,16 +516,15 @@
           <t>Agroquímicos Sur SpA</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" s="5" t="n">
         <v>46267</v>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="F2" s="5" t="n">
         <v>46297</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>2380000</v>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>Fungicidas</t>
@@ -543,7 +542,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>77.123.456-7</t>
+          <t>77.123.456-9</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -551,17 +550,15 @@
           <t>Agroquímicos Sur SpA</t>
         </is>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E3" s="5" t="n">
         <v>46282</v>
       </c>
-      <c r="F3" s="2" t="n">
+      <c r="F3" s="5" t="n">
         <v>46312</v>
       </c>
       <c r="G3" s="3" t="n">
         <v>1150000</v>
       </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -574,7 +571,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>76.987.654-3</t>
+          <t>76.987.654-5</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -582,17 +579,15 @@
           <t>Combustibles Araucanía Ltda.</t>
         </is>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="E4" s="5" t="n">
         <v>46272</v>
       </c>
-      <c r="F4" s="2" t="n">
+      <c r="F4" s="5" t="n">
         <v>46302</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>4520000</v>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -605,7 +600,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>76.987.654-3</t>
+          <t>76.987.654-5</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -613,16 +608,15 @@
           <t>Combustibles Araucanía Ltda.</t>
         </is>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="E5" s="5" t="n">
         <v>46284</v>
       </c>
-      <c r="F5" s="2" t="n">
+      <c r="F5" s="5" t="n">
         <v>46302</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>-320000</v>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>Nota de crédito</t>
